--- a/Final Project/Final Submission/PowerBI File.xlsx
+++ b/Final Project/Final Submission/PowerBI File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thilber2\InteractiveData202610\Final Project\Final Submission\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41152ADD-53A8-496F-97BF-6ACB252CC938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468EC203-6ABA-4DF9-9BFE-CB2F48D84F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-14150" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -208,30 +208,6 @@
 &lt;div id="plotly-div"&gt;&lt;/div&gt;
 &lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
 &lt;script&gt;
-var fig = {"data":[{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#CCFFCC","#CCFFCC","#CCFFCC","#CCFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"font":{"size":12},"line":{"color":"black"},"values":[["ARCH 22860","ARCS 12721","ID 19670","ID 19883","CMGT 19400","ARCH 13310","ARCH 14775","ARCS 11014","CMGT 17964","AED 22860","CMGT 16841","ARCH 16841","ARCH 29604","ARCH 19059","ID 15409","ARCH 15217","CMGT 11015","ID 13889","ID 29543","CMGT 21745","ARCH 14841"],[22.0,10.0,56.0,68.0,97.0,98.0,84.0,12.0,103.0,11.0,68.0,348.0,87.0,27.0,61.0,152.0,39.0,57.0,68.0,129.0,101.0],[1.0,0.0,5.0,4.0,8.0,9.0,6.0,2.0,12.0,1.0,6.0,43.0,11.0,5.0,11.0,18.0,5.0,8.0,9.0,23.0,18.0],[1.0,1.0,2.0,5.0,5.0,6.0,7.0,0.0,6.0,1.0,7.0,26.0,7.0,1.0,3.0,17.0,4.0,6.0,8.0,10.0,9.0],[20.0,9.0,49.0,59.0,84.0,83.0,71.0,10.0,85.0,9.0,55.0,279.0,69.0,21.0,47.0,117.0,30.0,43.0,51.0,96.0,74.0],["90.91%","90.00%","87.50%","86.76%","86.60%","84.69%","84.52%","83.33%","82.52%","81.82%","80.88%","80.17%","79.31%","77.78%","77.05%","76.97%","76.92%","75.44%","75.00%","74.42%","73.27%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":true,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFCC"]]},"line":{"color":"black"},"values":[["AED 22860"],[11.0],[1.0],[1.0],[9.0],["81.82%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"lightslategray"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["ARCH 22860","ARCH 13310","ARCH 14775","ARCH 16841","ARCH 29604","ARCH 19059","ARCH 15217","ARCH 14841"],[22.0,98.0,84.0,348.0,87.0,27.0,152.0,101.0],[1.0,9.0,6.0,43.0,11.0,5.0,18.0,18.0],[1.0,6.0,7.0,26.0,7.0,1.0,17.0,9.0],[20.0,83.0,71.0,279.0,69.0,21.0,117.0,74.0],["90.91%","84.69%","84.52%","80.17%","79.31%","77.78%","76.97%","73.27%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"lightslategray"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#FFFFCC"]]},"line":{"color":"black"},"values":[["ARCS 12721","ARCS 11014"],[10.0,12.0],[0.0,2.0],[1.0,0.0],[9.0,10.0],["90.00%","83.33%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"lightslategray"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["CMGT 19400","CMGT 17964","CMGT 16841","CMGT 11015","CMGT 21745"],[97.0,103.0,68.0,39.0,129.0],[8.0,12.0,6.0,5.0,23.0],[5.0,6.0,7.0,4.0,10.0],[84.0,85.0,55.0,30.0,96.0],["86.60%","82.52%","80.88%","76.92%","74.42%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"lightslategray"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#CCFFCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["ID 19670","ID 19883","ID 15409","ID 13889","ID 29543"],[56.0,68.0,61.0,57.0,68.0],[5.0,4.0,11.0,8.0,9.0],[2.0,5.0,3.0,6.0,8.0],[49.0,59.0,47.0,43.0,51.0],["87.50%","86.76%","77.05%","75.44%","75.00%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"lightslategray"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"}],"layout":{"height":650,"title":{"font":{"color":"black","size":24,"weight":"bold"},"text":"\u003cb\u003eSpring 2026 CAED Midterm Report","x":0.5,"xanchor":"center","y":0.965,"yanchor":"top"},"width":1200,"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}},"font":{"family":"Segoe UI"},"updatemenus":[{"buttons":[{"args":[{"visible":[true,false,false,false,false,false]}],"label":"All","method":"update"},{"args":[{"visible":[false,true,false,false,false,false]}],"label":"AED","method":"update"},{"args":[{"visible":[false,false,true,false,false,false]}],"label":"ARCH","method":"update"},{"args":[{"visible":[false,false,false,true,false,false]}],"label":"ARCS","method":"update"},{"args":[{"visible":[false,false,false,false,true,false]}],"label":"CMGT","method":"update"},{"args":[{"visible":[false,false,false,false,false,true]}],"label":"ID","method":"update"}],"direction":"down","showactive":true,"type":"dropdown","x":0.5,"xanchor":"center","y":1.1,"yanchor":"top"}],"annotations":[{"showarrow":false,"text":"\u003cb\u003eSubject:\u003c\u002fb\u003e","x":0.435,"xanchor":"center","y":1.0875,"yanchor":"top","font":{"size":14,"color":"black"}}]}};
-function renderPlot() {
-    var container = document.getElementById('plotly-div');
-    if (container) {
-        Plotly.newPlot(container, fig.data, fig.layout, {responsive: true});
-    }
-}
-// Initial render
-setTimeout(renderPlot, 300);
-// Re-render if Power BI wipes it
-setInterval(function() {
-    var container = document.getElementById('plotly-div');
-    if (container &amp;&amp; container.children.length === 0) {
-        renderPlot();
-    }
-}, 2000);
-&lt;/script&gt;
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-&lt;div id="plotly-div"&gt;&lt;/div&gt;
-&lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
-&lt;script&gt;
 var fig = {"data":[{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#CCFFCC","#CCFFCC","#CCFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"font":{"size":12},"line":{"color":"black"},"values":[["MDJ 12062","VCD 17656","CCI 11716","VCD 18414","MDJ 13358","EMAT 12670","VCD 24327","MDJ 25946","MDJ 25865","VCD 28950","VCD 25988","COMM 17591","MDJ 15027","MDJ 28436","VCD 18839","VCD 19588","EMAT 19538","MDJ 28950","VCD 13182","COMM 21241","EMAT 26013","MDJ 28984","MDJ 21449","MDJ 22796","MDJ 20627","EMAT 17213"],[20.0,18.0,86.0,33.0,102.0,24.0,66.0,59.0,39.0,36.0,46.0,662.0,408.0,40.0,100.0,85.0,166.0,32.0,50.0,55.0,58.0,93.0,36.0,40.0,97.0,30.0],[0.0,0.0,9.0,3.0,11.0,2.0,8.0,6.0,4.0,3.0,7.0,63.0,40.0,5.0,14.0,10.0,24.0,6.0,9.0,9.0,7.0,18.0,2.0,7.0,14.0,4.0],[1.0,1.0,1.0,2.0,5.0,2.0,3.0,4.0,3.0,4.0,2.0,67.0,41.0,3.0,6.0,7.0,10.0,1.0,2.0,4.0,7.0,5.0,7.0,4.0,14.0,5.0],[19.0,17.0,76.0,28.0,86.0,20.0,55.0,49.0,32.0,29.0,37.0,532.0,327.0,32.0,80.0,68.0,132.0,25.0,39.0,42.0,44.0,70.0,27.0,29.0,69.0,21.0],["95.00%","94.44%","88.37%","84.85%","84.31%","83.33%","83.33%","83.05%","82.05%","80.56%","80.43%","80.36%","80.15%","80.00%","80.00%","80.00%","79.52%","78.12%","78.00%","76.36%","75.86%","75.27%","75.00%","72.50%","71.13%","70.00%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":true,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#CCFFCC"]]},"line":{"color":"black"},"values":[["CCI 11716"],[86.0],[9.0],[1.0],[76.0],["88.37%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["COMM 17591","COMM 21241"],[662.0,55.0],[63.0,9.0],[67.0,4.0],[532.0,42.0],["80.36%","76.36%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["EMAT 12670","EMAT 19538","EMAT 26013","EMAT 17213"],[24.0,166.0,58.0,30.0],[2.0,24.0,7.0,4.0],[2.0,10.0,7.0,5.0],[20.0,132.0,44.0,21.0],["83.33%","79.52%","75.86%","70.00%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#CCFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["MDJ 12062","MDJ 13358","MDJ 25946","MDJ 25865","MDJ 15027","MDJ 28436","MDJ 28950","MDJ 28984","MDJ 21449","MDJ 22796","MDJ 20627"],[20.0,102.0,59.0,39.0,408.0,40.0,32.0,93.0,36.0,40.0,97.0],[0.0,11.0,6.0,4.0,40.0,5.0,6.0,18.0,2.0,7.0,14.0],[1.0,5.0,4.0,3.0,41.0,3.0,1.0,5.0,7.0,4.0,14.0],[19.0,86.0,49.0,32.0,327.0,32.0,25.0,70.0,27.0,29.0,69.0],["95.00%","84.31%","83.05%","82.05%","80.15%","80.00%","78.12%","75.27%","75.00%","72.50%","71.13%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC"],["#CCFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["VCD 17656","VCD 18414","VCD 24327","VCD 28950","VCD 25988","VCD 18839","VCD 19588","VCD 13182"],[18.0,33.0,66.0,36.0,46.0,100.0,85.0,50.0],[0.0,3.0,8.0,3.0,7.0,14.0,10.0,9.0],[1.0,2.0,3.0,4.0,2.0,6.0,7.0,2.0],[17.0,28.0,55.0,29.0,37.0,80.0,68.0,39.0],["94.44%","84.85%","83.33%","80.56%","80.43%","80.00%","80.00%","78.00%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"}],"layout":{"height":650,"title":{"font":{"color":"black","size":24,"weight":"bold"},"text":"\u003cb\u003eSpring 2026 CCI Midterm Report","x":0.5,"xanchor":"center","y":0.965,"yanchor":"top"},"width":1200,"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}},"font":{"family":"Segoe UI"},"updatemenus":[{"buttons":[{"args":[{"visible":[true,false,false,false,false,false]}],"label":"All","method":"update"},{"args":[{"visible":[false,true,false,false,false,false]}],"label":"CCI","method":"update"},{"args":[{"visible":[false,false,true,false,false,false]}],"label":"COMM","method":"update"},{"args":[{"visible":[false,false,false,true,false,false]}],"label":"EMAT","method":"update"},{"args":[{"visible":[false,false,false,false,true,false]}],"label":"MDJ","method":"update"},{"args":[{"visible":[false,false,false,false,false,true]}],"label":"VCD","method":"update"}],"direction":"down","showactive":true,"type":"dropdown","x":0.5,"xanchor":"center","y":1.1,"yanchor":"top"}],"annotations":[{"showarrow":false,"text":"\u003cb\u003eSchool:\u003c\u002fb\u003e","x":0.435,"xanchor":"center","y":1.0875,"yanchor":"top","font":{"size":14,"color":"black"}}]}};
 function renderPlot() {
     var container = document.getElementById('plotly-div');
@@ -1000,30 +976,6 @@
 &lt;div id="plotly-div"&gt;&lt;/div&gt;
 &lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
 &lt;script&gt;
-var fig = {"data":[{"cells":{"fill":{"color":[["#FFFFFF","#E3E6E8","#EFAB00"],["#FFFFFF","#E3E6E8","#EFAB00"],["#FFFFFF","#E3E6E8","#EFAB00"]]},"font":{"color":"black"},"line":{"color":"black"},"values":[[1,2," "],["CAED Major, FR or SO, CAED Course, midterm D+ or below, still registered","CAED Major, JR or SR, CAED Course, midterm F, still registered","Total"],[[84],[14],[98]]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","weight":"bold"},"line":{"color":"black"},"values":["Group #","CAED Midterm Intervention - Student Criteria","# of Instances"]},"visible":true,"type":"table"}],"layout":{"font":{"family":"Segoe UI"},"height":280,"margin":{"b":20,"l":20,"r":20,"t":80},"title":{"font":{"color":"black","size":24,"weight":"bold"},"text":"\u003cb\u003eSpring 2026 CAED Advisor Intervention Table","x":0.5,"xanchor":"center"},"width":700,"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}}}};
-function renderPlot() {
-    var container = document.getElementById('plotly-div');
-    if (container) {
-        Plotly.newPlot(container, fig.data, fig.layout, {responsive: true});
-    }
-}
-// Initial render
-setTimeout(renderPlot, 300);
-// Re-render if Power BI wipes it
-setInterval(function() {
-    var container = document.getElementById('plotly-div');
-    if (container &amp;&amp; container.children.length === 0) {
-        renderPlot();
-    }
-}, 2000);
-&lt;/script&gt;
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-&lt;div id="plotly-div"&gt;&lt;/div&gt;
-&lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
-&lt;script&gt;
 var fig = {"data":[{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#EFAB00"],["#FFFFFF","#FFF1CC","#EFAB00"],["#FFFFFF","#FFF1CC","#EFAB00"]]},"font":{"color":"black"},"line":{"color":"black"},"values":[[1,2," "],["CCI Major, FR or SO, CAED Course, midterm D+ or Below, still registered","CCI Major, JR or SR, CAED Course, midterm F, still registered","Total"],[[72],[19],[91]]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","weight":"bold"},"line":{"color":"black"},"values":["Group #","CCI Midterm Intervention - Student Criteria","# of Instances"]},"visible":true,"type":"table"}],"layout":{"font":{"family":"Segoe UI"},"height":280,"margin":{"b":20,"l":20,"r":20,"t":80},"title":{"font":{"color":"black","size":24,"weight":"bold"},"text":"\u003cb\u003eSpring 2026 CCI Advisor Intervention Table","x":0.5,"xanchor":"center"},"width":700,"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}}}};
 function renderPlot() {
     var container = document.getElementById('plotly-div');
@@ -1120,30 +1072,6 @@
 &lt;div id="plotly-div"&gt;&lt;/div&gt;
 &lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
 &lt;script&gt;
-var fig = {"data":[{"customdata":["Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of D+ or lower"],"hovertemplate":"\u003cb\u003eFR\u002fSO Interventions\u003c\u002fb\u003e\u003cbr\u003eTerm: %{x}\u003cbr\u003e# of Interventions Needed: %{y}\u003cbr\u003e%{customdata}\u003cextra\u003e\u003c\u002fextra\u003e","line":{"color":"#003976","width":2},"name":"FR\u002fSO Interventions Needed","x":["Fall 2022","Spring 2023","Fall 2023","Spring 2024","Fall 2024","Spring 2025","Fall 2025","Spring 2026"],"y":[424,392,442,404,406,363,417,268],"type":"scatter"},{"hovertemplate":"\u003cb\u003eJR\u002fSR Interventions\u003c\u002fb\u003e\u003cbr\u003eTerm: %{x}\u003cbr\u003e# of Interventions Needed: %{y}\u003cbr\u003eCriteria: MT Grade of F\u003cextra\u003e\u003c\u002fextra\u003e","line":{"color":"#EFAB00","width":2},"name":"JR\u002fSR Interventions Needed","x":["Fall 2022","Spring 2023","Fall 2023","Spring 2024","Fall 2024","Spring 2025","Fall 2025","Spring 2026"],"y":[37,35,30,38,51,46,24,40],"type":"scatter"},{"hovertemplate":"\u003cb\u003eTotal Number of Interventions\u003c\u002fb\u003e\u003cbr\u003eTerm: %{x}\u003cbr\u003e# of Interventions: %{text}\u003cextra\u003e\u003c\u002fextra\u003e","mode":"text","name":"Total Interventions (n)","showlegend":true,"text":["461","427","472","442","457","409","441","308"],"textfont":{"weight":"bold"},"x":["Fall 2022","Spring 2023","Fall 2023","Spring 2024","Fall 2024","Spring 2025","Fall 2025","Spring 2026"],"y":[-12,-12,-12,-12,-12,-12,-12,-12],"type":"scatter"}],"layout":{"font":{"family":"Segoe UI"},"legend":{"orientation":"h","title":{"font":{"color":"black"},"text":"\u003cb\u003eLegend:\u003c\u002fb\u003e"},"x":0.5,"xanchor":"center","y":-0.4,"yanchor":"bottom"},"title":{"font":{"color":"black","size":24},"text":"\u003cb\u003eCotA Interventions Needed Over Time\u003c\u002fb\u003e","x":0.5,"xanchor":"center","y":0.93,"yanchor":"top"},"xaxis":{"title":{"font":{"size":18},"text":"\u003ci\u003eSemester\u003c\u002fi\u003e"}},"yaxis":{"dtick":75,"range":[-20,475],"title":{"font":{"size":18},"text":"\u003ci\u003e# of Intervention\u003c\u002fi\u003e"}},"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}},"margin":{"l":20,"r":20,"b":20,"t":80},"shapes":[{"fillcolor":"white","layer":"below","line":{"color":"black","width":1},"type":"rect","x0":0,"x1":1,"xref":"paper","y0":-19,"y1":10,"yref":"y"}],"height":350,"width":1200,"annotations":[{"ax":0,"ay":-40,"font":{"size":10},"text":"Change in\u003cbr\u003eFR\u002fSO Criteria","x":7,"y":268}]}};
-function renderPlot() {
-    var container = document.getElementById('plotly-div');
-    if (container) {
-        Plotly.newPlot(container, fig.data, fig.layout, {responsive: true});
-    }
-}
-// Initial render
-setTimeout(renderPlot, 300);
-// Re-render if Power BI wipes it
-setInterval(function() {
-    var container = document.getElementById('plotly-div');
-    if (container &amp;&amp; container.children.length === 0) {
-        renderPlot();
-    }
-}, 2000);
-&lt;/script&gt;
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-&lt;div id="plotly-div"&gt;&lt;/div&gt;
-&lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
-&lt;script&gt;
 var fig = {"data":[{"colorbar":{"title":{"font":{"color":"black"},"text":"\u003cb\u003eStudent Density\u003c\u002fb\u003e"}},"colorscale":[[0.0,"#013271"],[0.1,"#5E636E"],[0.25,"#9D9576"],[1.0,"#E7D150"]],"hovertemplate":"\u003cb\u003eSector Details\u003c\u002fb\u003e\u003cbr\u003eMid Term Grade: %{x}\u003cbr\u003eFinal Grade: %{y}\u003cbr\u003e# of Students: %{z}\u003cextra\u003e\u003c\u002fextra\u003e","visible":true,"x":["0.0","1.0","1.3","1.7","2.0","2.3","2.7","3.0","3.3","3.7","4.0"],"xgap":1,"y":["0.0","1.0","1.3","1.7","2.0","2.3","2.7","3.0","3.3","3.7","4.0"],"ygap":1,"z":[[3,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,1,0,0,1,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[2,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,1,1,0,0],[0,0,0,0,1,1,0,3,0,0,0],[0,1,0,0,0,1,0,0,0,0,0],[0,0,0,0,0,0,1,0,0,0,0],[0,0,0,0,0,1,0,1,1,1,0],[1,0,0,0,1,0,1,1,4,5,4],[0,0,0,0,1,0,0,0,1,4,29]],"zmax":26,"zmin":0,"type":"heatmap"},{"colorbar":{"title":{"font":{"color":"black"},"text":"\u003cb\u003eStudent Density\u003c\u002fb\u003e"}},"colorscale":[[0.0,"#013271"],[0.1,"#5E636E"],[0.25,"#9D9576"],[1.0,"#E7D150"]],"hovertemplate":"\u003cb\u003eSector Details\u003c\u002fb\u003e\u003cbr\u003eMid Term Grade: %{x}\u003cbr\u003eFinal Grade: %{y}\u003cbr\u003e# of Students: %{z}\u003cextra\u003e\u003c\u002fextra\u003e","visible":false,"x":["0.0","1.0","1.3","1.7","2.0","2.3","2.7","3.0","3.3","3.7","4.0"],"xgap":1,"y":["0.0","1.0","1.3","1.7","2.0","2.3","2.7","3.0","3.3","3.7","4.0"],"ygap":1,"z":[[1,1,0,0,0,0,0,3,2,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,1,0,0,0,0,0],[0,0,0,1,0,1,0,0,0,0,1],[1,1,0,0,1,0,0,1,0,0,2],[0,0,0,0,0,1,0,0,0,1,1],[0,0,0,1,3,1,1,1,0,0,0],[0,0,0,0,0,1,0,3,1,1,3],[0,0,0,0,0,0,0,2,2,1,1],[0,0,0,0,0,0,0,3,2,1,4],[0,0,0,0,0,0,2,0,2,5,26]],"zmax":26,"zmin":0,"type":"heatmap"},{"line":{"color":"#FF8C00","dash":"dash","width":2},"mode":"lines","name":"Intervention Eligible","showlegend":true,"x":[null],"y":[null],"type":"scatter"}],"layout":{"font":{"family":"Segoe UI"},"height":550,"legend":{"orientation":"h","x":0.5,"xanchor":"center","y":-0.15,"yanchor":"top"},"plot_bgcolor":"black","title":{"font":{"color":"black","size":24},"text":"\u003cb\u003eAED Grade Movement from Midterms to Final\u003c\u002fb\u003e","x":0.5,"xanchor":"center","y":0.96,"yanchor":"top"},"updatemenus":[{"buttons":[{"args":[{"z":[[[3,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,1,0,0,1,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[2,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,1,1,0,0],[0,0,0,0,1,1,0,3,0,0,0],[0,1,0,0,0,1,0,0,0,0,0],[0,0,0,0,0,0,1,0,0,0,0],[0,0,0,0,0,1,0,1,1,1,0],[1,0,0,0,1,0,1,1,4,5,4],[0,0,0,0,1,0,0,0,1,4,29]]],"zmin":[0],"zmax":[29]}],"label":"Fall 2025","method":"update"},{"args":[{"z":[[[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,1,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,1,0,0],[0,0,0,0,0,0,0,0,0,1,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,1,0],[0,0,0,0,0,0,0,1,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,4]]],"zmin":[0],"zmax":[4]}],"label":"Spring 2025","method":"update"},{"args":[{"z":[[[5,0,0,0,0,0,0,2,0,0,0],[1,0,0,1,0,0,0,0,0,0,0],[0,0,0,0,0,1,0,0,0,0,0],[0,0,0,1,1,0,0,0,0,0,1],[0,0,0,0,1,0,0,0,0,0,0],[0,0,0,1,0,0,0,1,0,0,0],[0,0,0,0,2,2,0,1,0,0,0],[0,0,0,0,0,1,1,4,1,0,2],[0,1,0,0,0,0,0,1,1,1,4],[0,0,0,0,0,0,1,3,1,3,5],[0,0,0,0,0,0,0,1,2,2,25]]],"zmin":[0],"zmax":[25]}],"label":"Fall 2024","method":"update"},{"args":[{"z":[[[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,2,0],[0,0,0,0,0,0,0,0,0,0,4]]],"zmin":[0],"zmax":[4]}],"label":"Spring 2024","method":"update"},{"args":[{"z":[[[5,0,0,0,0,1,0,0,0,1,0],[0,0,0,0,0,0,0,0,0,0,0],[1,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,1,1,1,0,0],[1,0,0,0,0,0,1,0,0,0,0],[0,0,0,1,1,0,0,0,0,0,0],[0,0,1,0,0,0,0,1,1,1,0],[0,0,0,0,0,0,0,3,0,1,1],[0,0,0,0,0,0,1,2,1,1,0],[0,0,0,1,0,0,0,2,2,1,1],[2,0,0,0,0,0,1,0,0,0,23]]],"zmin":[0],"zmax":[23]}],"label":"Fall 2023","method":"update"},{"args":[{"z":[[[2,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,1,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[1,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,1,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,1,0],[0,0,0,0,0,1,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,0,0,0,0,0,1]]],"zmin":[0],"zmax":[2]}],"label":"Spring 2023","method":"update"},{"args":[{"z":[[[1,1,0,0,0,0,0,3,2,0,0],[0,0,0,0,0,0,0,0,0,0,0],[0,0,0,0,0,1,0,0,0,0,0],[0,0,0,1,0,1,0,0,0,0,1],[1,1,0,0,1,0,0,1,0,0,2],[0,0,0,0,0,1,0,0,0,1,1],[0,0,0,1,3,1,1,1,0,0,0],[0,0,0,0,0,1,0,3,1,1,3],[0,0,0,0,0,0,0,2,2,1,1],[0,0,0,0,0,0,0,3,2,1,4],[0,0,0,0,0,0,2,0,2,5,26]]],"zmin":[0],"zmax":[26]}],"label":"Fall 2022","method":"update"}],"direction":"down","showactive":true,"x":0.575,"xanchor":"center","y":1.135,"yanchor":"top"}],"width":730,"xaxis":{"showgrid":false,"title":{"font":{"size":18},"text":"\u003ci\u003eMid Term Grades\u003c\u002fi\u003e"}},"yaxis":{"showgrid":false,"title":{"font":{"size":18},"text":"\u003ci\u003eFinal Grades\u003c\u002fi\u003e"}},"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}},"annotations":[{"font":{"color":"black","size":16},"showarrow":false,"text":"\u003cb\u003eSemester:\u003c\u002fb\u003e","x":0.3925,"xref":"paper","y":1.1275,"yref":"paper"}],"shapes":[{"layer":"above","line":{"color":"#FF8C00","dash":"dash","width":2},"type":"rect","x0":-0.5,"x1":4.5,"y0":-0.5,"y1":10.5}]}};
 function renderPlot() {
     var container = document.getElementById('plotly-div');
@@ -1553,6 +1481,78 @@
 &lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
 &lt;script&gt;
 var fig = {"data":[{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#CCFFCC","#CCFFCC","#CCFFCC","#CCFFCC","#CCFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#CCFFCC","#FFCCCC","#B1B1B1","#FFCCCC","#B1B1B1","#B1B1B1","#B1B1B1","#B1B1B1","#B1B1B1","#B1B1B1"]]},"font":{"color":"black"},"line":{"color":"black"},"values":[["A","A-","B+","B","B-","C+","C","C-","D+","D","F","S","U","W","SF","NF","AU","NaN","DR","IN","NR"],[4.0,3.7,3.3,3.0,2.7,2.3,2.0,1.7,1.3,1.0,0.0,4.0,0.0,0.0,0.0,"NaN","NaN","NaN","NaN","NaN","NaN"],["Passing Grade - No Intervention Needed","Passing Grade - No Intervention Needed","Passing Grade - No Intervention Needed","Passing Grade - No Intervention Needed","Passing Grade - No Intervention Needed","Passing Grade - No Intervention Needed","Intervention Required (FR\u002fSO Only)","Intervention Required (FR\u002fSO Only)","Intervention Required (FR\u002fSO Only)","Intervention Required (FR\u002fSO Only)","Intervention Required","Passing Grade - No Intervention Needed","Intervention Required","No Intervention (Withdrawn)","Intervention Required","No Grade Reported","No Grade Reported","No Grade Reported","No Grade Reported","No Grade Reported","No Grade Reported"]]},"columnwidth":[1,1,4],"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","weight":"bold"},"line":{"color":"black"},"values":["Letter Grade","GPA Conversion","Intervention Needed"]},"type":"table"}],"layout":{"font":{"family":"Segoe UI"},"height":540,"margin":{"b":20,"l":20,"r":20,"t":50},"title":{"font":{"color":"black","size":20},"text":"\u003cb\u003eGPA Conversion Chart\u003c\u002fb\u003e","x":0.5,"xanchor":"center"},"width":450,"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}}}};
+function renderPlot() {
+    var container = document.getElementById('plotly-div');
+    if (container) {
+        Plotly.newPlot(container, fig.data, fig.layout, {responsive: true});
+    }
+}
+// Initial render
+setTimeout(renderPlot, 300);
+// Re-render if Power BI wipes it
+setInterval(function() {
+    var container = document.getElementById('plotly-div');
+    if (container &amp;&amp; container.children.length === 0) {
+        renderPlot();
+    }
+}, 2000);
+&lt;/script&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+&lt;div id="plotly-div"&gt;&lt;/div&gt;
+&lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
+&lt;script&gt;
+var fig = {"data":[{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#CCFFCC","#CCFFCC","#CCFFCC","#CCFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"font":{"size":12},"line":{"color":"black"},"values":[["ARCH 22860","ARCS 12721","ID 19670","ID 19883","CMGT 19400","ARCH 13310","ARCH 14775","ARCS 11014","CMGT 17964","AED 22860","CMGT 16841","ARCH 16841","ARCH 29604","ARCH 19059","ID 15409","ARCH 15217","CMGT 11015","ID 13889","ID 29543","CMGT 21745","ARCH 14841"],[22.0,10.0,56.0,68.0,97.0,98.0,84.0,12.0,103.0,11.0,68.0,348.0,87.0,27.0,61.0,152.0,39.0,57.0,68.0,129.0,101.0],[1.0,0.0,5.0,4.0,8.0,9.0,6.0,2.0,12.0,1.0,6.0,43.0,11.0,5.0,11.0,18.0,5.0,8.0,9.0,23.0,18.0],[1.0,1.0,2.0,5.0,5.0,6.0,7.0,0.0,6.0,1.0,7.0,26.0,7.0,1.0,3.0,17.0,4.0,6.0,8.0,10.0,9.0],[20.0,9.0,49.0,59.0,84.0,83.0,71.0,10.0,85.0,9.0,55.0,279.0,69.0,21.0,47.0,117.0,30.0,43.0,51.0,96.0,74.0],["90.91%","90.00%","87.50%","86.76%","86.60%","84.69%","84.52%","83.33%","82.52%","81.82%","80.88%","80.17%","79.31%","77.78%","77.05%","76.97%","76.92%","75.44%","75.00%","74.42%","73.27%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":true,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFCC"]]},"line":{"color":"black"},"values":[["AED 22860"],[11.0],[1.0],[1.0],[9.0],["81.82%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["ARCH 22860","ARCH 13310","ARCH 14775","ARCH 16841","ARCH 29604","ARCH 19059","ARCH 15217","ARCH 14841"],[22.0,98.0,84.0,348.0,87.0,27.0,152.0,101.0],[1.0,9.0,6.0,43.0,11.0,5.0,18.0,18.0],[1.0,6.0,7.0,26.0,7.0,1.0,17.0,9.0],[20.0,83.0,71.0,279.0,69.0,21.0,117.0,74.0],["90.91%","84.69%","84.52%","80.17%","79.31%","77.78%","76.97%","73.27%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#FFFFCC"]]},"line":{"color":"black"},"values":[["ARCS 12721","ARCS 11014"],[10.0,12.0],[0.0,2.0],[1.0,0.0],[9.0,10.0],["90.00%","83.33%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["CMGT 19400","CMGT 17964","CMGT 16841","CMGT 11015","CMGT 21745"],[97.0,103.0,68.0,39.0,129.0],[8.0,12.0,6.0,5.0,23.0],[5.0,6.0,7.0,4.0,10.0],[84.0,85.0,55.0,30.0,96.0],["86.60%","82.52%","80.88%","76.92%","74.42%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#CCFFCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["ID 19670","ID 19883","ID 15409","ID 13889","ID 29543"],[56.0,68.0,61.0,57.0,68.0],[5.0,4.0,11.0,8.0,9.0],[2.0,5.0,3.0,6.0,8.0],[49.0,59.0,47.0,43.0,51.0],["87.50%","86.76%","77.05%","75.44%","75.00%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"}],"layout":{"height":650,"title":{"font":{"color":"black","size":24,"weight":"bold"},"text":"\u003cb\u003eSpring 2026 CAED Midterm Report","x":0.5,"xanchor":"center","y":0.965,"yanchor":"top"},"width":1200,"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}},"font":{"family":"Segoe UI"},"updatemenus":[{"buttons":[{"args":[{"visible":[true,false,false,false,false,false]}],"label":"All","method":"update"},{"args":[{"visible":[false,true,false,false,false,false]}],"label":"AED","method":"update"},{"args":[{"visible":[false,false,true,false,false,false]}],"label":"ARCH","method":"update"},{"args":[{"visible":[false,false,false,true,false,false]}],"label":"ARCS","method":"update"},{"args":[{"visible":[false,false,false,false,true,false]}],"label":"CMGT","method":"update"},{"args":[{"visible":[false,false,false,false,false,true]}],"label":"ID","method":"update"}],"direction":"down","showactive":true,"type":"dropdown","x":0.5,"xanchor":"center","y":1.1,"yanchor":"top"}],"annotations":[{"showarrow":false,"text":"\u003cb\u003eSubject:\u003c\u002fb\u003e","x":0.435,"xanchor":"center","y":1.0875,"yanchor":"top","font":{"size":14,"color":"black"}}]}};
+function renderPlot() {
+    var container = document.getElementById('plotly-div');
+    if (container) {
+        Plotly.newPlot(container, fig.data, fig.layout, {responsive: true});
+    }
+}
+// Initial render
+setTimeout(renderPlot, 300);
+// Re-render if Power BI wipes it
+setInterval(function() {
+    var container = document.getElementById('plotly-div');
+    if (container &amp;&amp; container.children.length === 0) {
+        renderPlot();
+    }
+}, 2000);
+&lt;/script&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+&lt;div id="plotly-div"&gt;&lt;/div&gt;
+&lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
+&lt;script&gt;
+var fig = {"data":[{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#EFAB00"],["#FFFFFF","#FFF1CC","#EFAB00"],["#FFFFFF","#FFF1CC","#EFAB00"]]},"font":{"color":"black"},"line":{"color":"black"},"values":[[1,2," "],["CAED Major, FR or SO, CAED Course, midterm D+ or below, still registered","CAED Major, JR or SR, CAED Course, midterm F, still registered","Total"],[[84],[14],[98]]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","weight":"bold"},"line":{"color":"black"},"values":["Group #","CAED Midterm Intervention - Student Criteria","# of Instances"]},"visible":true,"type":"table"}],"layout":{"font":{"family":"Segoe UI"},"height":280,"margin":{"b":20,"l":20,"r":20,"t":80},"title":{"font":{"color":"black","size":24,"weight":"bold"},"text":"\u003cb\u003eSpring 2026 CAED Advisor Intervention Table","x":0.5,"xanchor":"center"},"width":700,"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}}}};
+function renderPlot() {
+    var container = document.getElementById('plotly-div');
+    if (container) {
+        Plotly.newPlot(container, fig.data, fig.layout, {responsive: true});
+    }
+}
+// Initial render
+setTimeout(renderPlot, 300);
+// Re-render if Power BI wipes it
+setInterval(function() {
+    var container = document.getElementById('plotly-div');
+    if (container &amp;&amp; container.children.length === 0) {
+        renderPlot();
+    }
+}, 2000);
+&lt;/script&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+&lt;div id="plotly-div"&gt;&lt;/div&gt;
+&lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
+&lt;script&gt;
+var fig = {"data":[{"customdata":["Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of D+ or lower"],"hovertemplate":"\u003cb\u003eFR\u002fSO Interventions\u003c\u002fb\u003e\u003cbr\u003eTerm: %{x}\u003cbr\u003e# of Interventions Needed: %{y}\u003cbr\u003e%{customdata}\u003cextra\u003e\u003c\u002fextra\u003e","line":{"color":"#003976","width":2},"name":"FR\u002fSO Interventions Needed","x":["Fall 2022","Spring 2023","Fall 2023","Spring 2024","Fall 2024","Spring 2025","Fall 2025","Spring 2026"],"y":[424,392,442,404,406,363,417,268],"type":"scatter"},{"hovertemplate":"\u003cb\u003eJR\u002fSR Interventions\u003c\u002fb\u003e\u003cbr\u003eTerm: %{x}\u003cbr\u003e# of Interventions Needed: %{y}\u003cbr\u003eCriteria: MT Grade of F\u003cextra\u003e\u003c\u002fextra\u003e","line":{"color":"#EFAB00","width":2},"name":"JR\u002fSR Interventions Needed","x":["Fall 2022","Spring 2023","Fall 2023","Spring 2024","Fall 2024","Spring 2025","Fall 2025","Spring 2026"],"y":[37,35,30,38,51,46,24,40],"type":"scatter"},{"hovertemplate":"\u003cb\u003eTotal Number of Interventions\u003c\u002fb\u003e\u003cbr\u003eTerm: %{x}\u003cbr\u003e# of Interventions: %{text}\u003cextra\u003e\u003c\u002fextra\u003e","mode":"text","name":"Total Interventions (n)","showlegend":true,"text":["461","427","472","442","457","409","441","308"],"textfont":{"weight":"bold"},"x":["Fall 2022","Spring 2023","Fall 2023","Spring 2024","Fall 2024","Spring 2025","Fall 2025","Spring 2026"],"y":[-5,-5,-5,-5,-5,-5,-5,-5],"type":"scatter"}],"layout":{"font":{"family":"Segoe UI"},"legend":{"orientation":"h","title":{"font":{"color":"black"},"text":"\u003cb\u003eLegend:\u003c\u002fb\u003e"},"x":0.5,"xanchor":"center","y":-0.4,"yanchor":"bottom"},"title":{"font":{"color":"black","size":24},"text":"\u003cb\u003eCotA Interventions Needed Over Time\u003c\u002fb\u003e","x":0.5,"xanchor":"center","y":0.93,"yanchor":"top"},"xaxis":{"title":{"font":{"size":18},"text":"\u003ci\u003eSemester\u003c\u002fi\u003e"}},"yaxis":{"dtick":75,"range":[-20,475],"title":{"font":{"size":18},"text":"\u003ci\u003e# of Intervention\u003c\u002fi\u003e"}},"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}},"margin":{"l":20,"r":20,"b":20,"t":80},"shapes":[{"fillcolor":"white","layer":"below","line":{"color":"black","width":1},"type":"rect","x0":0,"x1":1,"xref":"paper","y0":-19,"y1":15,"yref":"y"}],"height":350,"width":1200,"annotations":[{"ax":0,"ay":-40,"font":{"size":10},"text":"Change in\u003cbr\u003eFR\u002fSO Criteria","x":7,"y":268}]}};
 function renderPlot() {
     var container = document.getElementById('plotly-div');
     if (container) {
@@ -2194,175 +2194,175 @@
         <v>58</v>
       </c>
       <c r="B2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" t="s">
         <v>59</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>60</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>61</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>62</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>63</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>64</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>65</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>66</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>67</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>68</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>69</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>70</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>71</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>72</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>74</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>75</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>76</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>77</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>78</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>79</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>80</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>81</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>82</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>83</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>84</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>85</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>86</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>87</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>88</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>89</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>90</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>91</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>92</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>93</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" t="s">
         <v>94</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AN2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO2" t="s">
         <v>95</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AP2" t="s">
         <v>96</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AQ2" t="s">
         <v>97</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AR2" t="s">
         <v>98</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AS2" t="s">
         <v>99</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AT2" t="s">
         <v>100</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AU2" t="s">
         <v>101</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AV2" t="s">
         <v>102</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AW2" t="s">
         <v>103</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AX2" t="s">
         <v>104</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AY2" t="s">
         <v>105</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AZ2" t="s">
         <v>106</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BA2" t="s">
         <v>107</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BB2" t="s">
         <v>108</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BC2" t="s">
         <v>109</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BD2" t="s">
         <v>110</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BE2" t="s">
         <v>111</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BF2" t="s">
         <v>112</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>
